--- a/Analysed/Gemini/Combined_Analysis_Summary_pro.xlsx
+++ b/Analysed/Gemini/Combined_Analysis_Summary_pro.xlsx
@@ -449,7 +449,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>4.1031 ± 2.6616</t>
+          <t>4.8630 ± 3.0013</t>
         </is>
       </c>
     </row>
@@ -461,7 +461,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>4.5827 ± 2.9735</t>
+          <t>5.3995 ± 3.2976</t>
         </is>
       </c>
     </row>
@@ -473,7 +473,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.4895 ± 0.3253</t>
+          <t>0.4447 ± 0.3067</t>
         </is>
       </c>
     </row>
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -819,20 +819,20 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>V1_5 divisions_per_second</t>
+          <t>V2_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="D14" t="n">
-        <v>7.462533333333331</v>
+        <v>8.613412698412699</v>
       </c>
       <c r="E14" t="n">
-        <v>8.151229191559597</v>
+        <v>9.249851092752532</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8648648648648649</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="15">
@@ -843,19 +843,115 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>V2_10 divisions_per_second</t>
+          <t>V3_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="C15" t="n">
+        <v>81</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3.253086419753086</v>
+      </c>
+      <c r="E15" t="n">
+        <v>3.736952941093936</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.2375</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>V4_1.7 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>57</v>
+      </c>
+      <c r="D16" t="n">
+        <v>8.797192982456142</v>
+      </c>
+      <c r="E16" t="n">
+        <v>9.678490530416838</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1607142857142857</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>V5_2.5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>48</v>
+      </c>
+      <c r="D17" t="n">
+        <v>9.42625</v>
+      </c>
+      <c r="E17" t="n">
+        <v>10.36665688638338</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.5531914893617021</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>V6_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>75</v>
+      </c>
+      <c r="D18" t="n">
+        <v>7.462533333333331</v>
+      </c>
+      <c r="E18" t="n">
+        <v>8.151229191559597</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.8648648648648649</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>linear</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>V7_10 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>50</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D19" t="n">
         <v>10.805</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E19" t="n">
         <v>12.50280168602222</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F19" t="n">
         <v>0.9183673469387755</v>
       </c>
     </row>
